--- a/data/trans_dic/P1419-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1419-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,81</t>
+          <t>1,46; 4,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,45</t>
+          <t>1,17; 4,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,0</t>
+          <t>2,16; 5,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 11,63</t>
+          <t>4,98; 11,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,65</t>
+          <t>1,6; 5,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,93</t>
+          <t>1,99; 6,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,26</t>
+          <t>5,43; 9,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,67</t>
+          <t>3,48; 6,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,47</t>
+          <t>0,79; 2,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,77</t>
+          <t>1,86; 4,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,34</t>
+          <t>4,15; 6,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,48</t>
+          <t>1,1; 4,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,22</t>
+          <t>0,25; 2,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,56</t>
+          <t>0,25; 2,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,92</t>
+          <t>1,93; 4,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 9,21</t>
+          <t>4,43; 9,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,54</t>
+          <t>3,11; 8,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,83</t>
+          <t>1,1; 4,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 10,15</t>
+          <t>6,45; 10,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,25</t>
+          <t>3,19; 6,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,38</t>
+          <t>1,82; 4,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,03</t>
+          <t>0,92; 3,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 6,81</t>
+          <t>4,33; 6,95</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,68</t>
+          <t>2,41; 5,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,58</t>
+          <t>0,65; 2,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,97</t>
+          <t>1,17; 3,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,1</t>
+          <t>4,04; 8,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 18,29</t>
+          <t>7,76; 17,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 11,97</t>
+          <t>5,12; 12,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 16,94</t>
+          <t>6,29; 16,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 23,94</t>
+          <t>14,87; 23,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,82</t>
+          <t>4,12; 7,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,8</t>
+          <t>2,07; 4,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,06</t>
+          <t>2,83; 6,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 10,42</t>
+          <t>7,74; 11,84</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,09</t>
+          <t>2,06; 3,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,16</t>
+          <t>1,25; 3,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,11</t>
+          <t>0,69; 2,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,38</t>
+          <t>4,09; 6,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 13,2</t>
+          <t>8,51; 13,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,34</t>
+          <t>4,6; 8,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,59</t>
+          <t>3,49; 6,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,74</t>
+          <t>8,8; 12,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,01</t>
+          <t>4,82; 6,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,75</t>
+          <t>2,88; 4,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,6</t>
+          <t>2,02; 3,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,75</t>
+          <t>6,49; 8,45</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,95</t>
+          <t>3,04; 8,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,03</t>
+          <t>0,2; 2,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,14</t>
+          <t>1,0; 3,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,23</t>
+          <t>1,36; 3,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,98</t>
+          <t>7,75; 12,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 12,87</t>
+          <t>8,26; 12,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 10,09</t>
+          <t>6,18; 10,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,18; 16,13</t>
+          <t>13,22; 17,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 10,19</t>
+          <t>6,41; 10,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,93</t>
+          <t>5,1; 8,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,69</t>
+          <t>3,99; 6,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,13</t>
+          <t>8,72; 11,46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,41; 15,42</t>
+          <t>11,28; 14,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,47; 13,32</t>
+          <t>9,44; 13,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,93</t>
+          <t>5,41; 8,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,42</t>
+          <t>7,55; 10,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 12,28</t>
+          <t>9,23; 12,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,54; 10,76</t>
+          <t>7,55; 10,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,14</t>
+          <t>4,37; 7,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,6</t>
+          <t>5,98; 8,64</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,74</t>
+          <t>2,45; 3,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,64</t>
+          <t>0,83; 1,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,0</t>
+          <t>1,16; 2,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,26</t>
+          <t>3,31; 4,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,89; 11,92</t>
+          <t>9,83; 11,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,43</t>
+          <t>7,52; 9,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 7,05</t>
+          <t>5,32; 6,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,3; 11,05</t>
+          <t>10,14; 11,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,35; 7,63</t>
+          <t>6,32; 7,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 5,49</t>
+          <t>4,35; 5,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 4,43</t>
+          <t>3,39; 4,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,52</t>
+          <t>6,99; 8,1</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>19043</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31822</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>54588</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7817; 22808</t>
+          <t>6900; 22208</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5551</t>
+          <t>0; 4313</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4667; 19083</t>
+          <t>5014; 19571</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9765; 25245</t>
+          <t>11876; 28873</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15579; 35660</t>
+          <t>15270; 35809</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4881; 17755</t>
+          <t>5041; 17904</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6489; 24054</t>
+          <t>6891; 22587</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23862; 41448</t>
+          <t>26498; 46155</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27096; 52043</t>
+          <t>27156; 52728</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5499; 18542</t>
+          <t>5908; 18929</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14516; 37031</t>
+          <t>14429; 35847</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37310; 60426</t>
+          <t>43125; 68837</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30594</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45008</t>
+          <t>50614</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4267; 16431</t>
+          <t>4050; 16514</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1047; 9280</t>
+          <t>1048; 9957</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>953; 9645</t>
+          <t>961; 9691</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8854; 22247</t>
+          <t>9317; 23877</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15944; 34257</t>
+          <t>16464; 35169</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10956; 28857</t>
+          <t>10501; 27720</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4193; 17989</t>
+          <t>4104; 18174</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23187; 38746</t>
+          <t>27254; 45556</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23399; 46188</t>
+          <t>23574; 46102</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13385; 33160</t>
+          <t>13758; 33634</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6968; 22686</t>
+          <t>6909; 22880</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35505; 56843</t>
+          <t>39213; 62982</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>27664</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31282</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56777</t>
+          <t>63064</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12927; 30809</t>
+          <t>13070; 30958</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4028; 16256</t>
+          <t>4087; 17133</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6124; 20727</t>
+          <t>6123; 20359</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9140; 47379</t>
+          <t>19029; 40285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12848; 30693</t>
+          <t>13024; 30098</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12725; 31126</t>
+          <t>13320; 31807</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9926; 28149</t>
+          <t>10452; 27432</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23933; 39962</t>
+          <t>27880; 44406</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29482; 55540</t>
+          <t>29246; 54210</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19682; 42729</t>
+          <t>18430; 42374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19240; 41693</t>
+          <t>19463; 42387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27177; 86913</t>
+          <t>50925; 77909</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52296</t>
+          <t>58453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>88754</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>130940</t>
+          <t>147207</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26162; 50673</t>
+          <t>25566; 49321</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14815; 36600</t>
+          <t>14513; 35527</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8470; 24260</t>
+          <t>7905; 24419</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39669; 66070</t>
+          <t>46284; 74726</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>61444; 94254</t>
+          <t>60814; 94185</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35622; 63795</t>
+          <t>35181; 64829</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28034; 54421</t>
+          <t>28847; 53877</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41651; 104988</t>
+          <t>75767; 103595</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94749; 136805</t>
+          <t>94051; 134946</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55398; 91328</t>
+          <t>55447; 90488</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40875; 71033</t>
+          <t>39851; 71211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>93355; 155849</t>
+          <t>129397; 168437</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12554</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>114602</t>
+          <t>126034</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>127156</t>
+          <t>139545</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10015; 27878</t>
+          <t>10645; 29140</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1037; 10342</t>
+          <t>1047; 11240</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5952; 19468</t>
+          <t>6234; 20436</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7605; 20060</t>
+          <t>7703; 22156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43541; 73813</t>
+          <t>44058; 73674</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62396; 97844</t>
+          <t>62772; 96195</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44138; 74483</t>
+          <t>45600; 77468</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>85415; 135357</t>
+          <t>109727; 142970</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>57260; 93632</t>
+          <t>58893; 94281</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65365; 100737</t>
+          <t>64786; 102391</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57008; 90972</t>
+          <t>54268; 90805</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>102551; 146192</t>
+          <t>121883; 160149</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>570</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>70996</t>
+          <t>76254</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71530</t>
+          <t>76825</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6626</t>
+          <t>0; 6260</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2977,52 +2977,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4633</t>
+          <t>0; 4389</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3289</t>
+          <t>0; 2955</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>142504; 192621</t>
+          <t>140885; 187049</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>105095; 147714</t>
+          <t>104704; 148746</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58559; 96676</t>
+          <t>58522; 95578</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>58911; 86856</t>
+          <t>63680; 92033</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>143660; 190029</t>
+          <t>142742; 190478</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>103816; 148124</t>
+          <t>103847; 148705</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60017; 97742</t>
+          <t>59841; 96440</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>59113; 86088</t>
+          <t>64670; 93368</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121254</t>
+          <t>134591</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>357940</t>
+          <t>397252</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>479194</t>
+          <t>531844</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>81215; 122441</t>
+          <t>80126; 120790</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28196; 56135</t>
+          <t>28402; 55647</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39502; 67595</t>
+          <t>39142; 70264</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>94178; 143855</t>
+          <t>113813; 156604</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>334234; 402735</t>
+          <t>332065; 403068</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>264533; 334297</t>
+          <t>266688; 333483</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>188189; 249091</t>
+          <t>187814; 246126</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>296506; 394680</t>
+          <t>368414; 427727</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>422146; 506949</t>
+          <t>419946; 504010</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>306667; 382766</t>
+          <t>303408; 377130</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>234530; 306153</t>
+          <t>234666; 306896</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>409223; 522293</t>
+          <t>494289; 572590</t>
         </is>
       </c>
     </row>
